--- a/outputs/evaluation/decision/v1/CF_M01/run_3/CF_M01_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M01/run_3/CF_M01_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,101 +471,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The objective of these services is to form a data lake where all history is stored so that it can be processed in the analytical module.</t>
+          <t>Aquestes tecnologies són les mateixes de les quals s’utilitzen actualment a l’empresa de Waapiti.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C_03, C_04, Capacity</t>
+          <t>Waapiti company standards</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AU_12, AU_16, AU_18, AU_19</t>
+          <t>AU_13, AU_14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12f. Capacity; 12g. Scalability; Capacity</t>
+          <t>Waapiti company standards</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cloud Storage Service; Amazon S3; Amazon Athena; AWS Glue</t>
+          <t>NestJS; TypeScript</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M01_AD01</t>
+          <t>CF_M01_AD07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
+          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6404</v>
+        <v>0.6361</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_07</t>
+          <t>AD_02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Being a serverless service, it is not necessary to manage the infrastructure when there is an increase in the set of data and users. In addition, to be able to obtain the data quickly, Athena performs the queries in parallel.</t>
+          <t>En el cas de la plataforma de Waapiti, l’arquitectura física no es correspon exactament a l’arquitectura lògica, ja que tant la capa de negoci com la capa de dades es divideixen en diversos serveis diferents. L’objectiu d’això és millorar la seguretat, l’escalabilitat i la disponibilitat del sistema.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C_01, Performance</t>
+          <t>C_02, seguretat, escalabilitat, disponibilitat</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_06, AU_07, AU_08, AU_09, AU_10, P_03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>42</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>12a. Speed and latency; Performance</t>
+          <t>12d. Availability and reliability; seguretat; escalabilitat; disponibilitat</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amazon Athena</t>
+          <t>API Gateway Service; Core Service; Analytical Module Service; Player API Service; Web Socket Service; API Gateway</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CF_M01_AD07</t>
+          <t>CF_M01_AD01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>To ensure the fastest possible data transmission, two Amazon services have been used, which allow us to perform a transmission in almost real time.</t>
+          <t>The goal of this is to improve the security, scalability, and availability of the system.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.6734</v>
+        <v>0.7478</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Això és degut de què es segueix el patró de disseny de microserveis Api Gateway. Aquest patró de disseny permet que solament un component sigui qui interactuï entre els usuaris i els serveis que proporciona la plataforma.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>C_05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_06, P_03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>15a. Access</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>API Gateway Service; API Gateway</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CF_M01_AD02</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Increases system security [...] It is only the Api Gateway that is responsible for authorization and SSL with the client</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.733</v>
       </c>
     </row>
   </sheetData>
